--- a/ig/DM-OCTOBRE-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="2409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="2421">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250919120000</t>
+    <t>20251017120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T12:00:00+01:00</t>
+    <t>2025-10-17T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7231,6 +7231,42 @@
   </si>
   <si>
     <t>Autodialyse assistée</t>
+  </si>
+  <si>
+    <t>1551</t>
+  </si>
+  <si>
+    <t>Accueil en unité protégée</t>
+  </si>
+  <si>
+    <t>1552</t>
+  </si>
+  <si>
+    <t>Rééducation par réalité virtuelle</t>
+  </si>
+  <si>
+    <t>1553</t>
+  </si>
+  <si>
+    <t>Rééducation de l’amputé</t>
+  </si>
+  <si>
+    <t>1554</t>
+  </si>
+  <si>
+    <t>Rééducation vestibulaire (trouble de l’équilibre)</t>
+  </si>
+  <si>
+    <t>1555</t>
+  </si>
+  <si>
+    <t>Rééducation du rachis</t>
+  </si>
+  <si>
+    <t>1556</t>
+  </si>
+  <si>
+    <t>Rééducation des paralysies cérébrales et polyhandicaps</t>
   </si>
   <si>
     <t/>
@@ -7501,7 +7537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1192"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -17033,15 +17069,63 @@
         <v>2406</v>
       </c>
       <c r="B1191" t="s" s="2">
-        <v>2406</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="s" s="2">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="B1192" t="s" s="2">
-        <v>2408</v>
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="s" s="2">
+        <v>2410</v>
+      </c>
+      <c r="B1193" t="s" s="2">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="s" s="2">
+        <v>2412</v>
+      </c>
+      <c r="B1194" t="s" s="2">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="s" s="2">
+        <v>2414</v>
+      </c>
+      <c r="B1195" t="s" s="2">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="s" s="2">
+        <v>2416</v>
+      </c>
+      <c r="B1196" t="s" s="2">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="s" s="2">
+        <v>2418</v>
+      </c>
+      <c r="B1197" t="s" s="2">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="s" s="2">
+        <v>2419</v>
+      </c>
+      <c r="B1198" t="s" s="2">
+        <v>2420</v>
       </c>
     </row>
   </sheetData>
